--- a/assets/templates/PHF_Payroll_Canonical_V1.xlsx
+++ b/assets/templates/PHF_Payroll_Canonical_V1.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
   <si>
     <t xml:space="preserve">Tên đơn vị: CÔNG TY CỔ PHẦN THỰC PHẨM PHÚ HOÀ</t>
   </si>
@@ -19,7 +19,7 @@
     <t xml:space="preserve">Địa chỉ: Trụ sở chính: 342 Phú Lợi, Phú Lợi, TP.HCM</t>
   </si>
   <si>
-    <t xml:space="preserve">BẢNG TÍNH - THANH TOÁN TIỀN LƯƠNG  NHÂN VIÊN [KỲ LƯƠNG]</t>
+    <t xml:space="preserve">BẢNG TÍNH - THANH TOÁN TIỀN LƯƠNG  NHÂN VIÊN</t>
   </si>
   <si>
     <t xml:space="preserve">Lần ban hành: …..</t>
@@ -28,7 +28,7 @@
     <t xml:space="preserve">MST:</t>
   </si>
   <si>
-    <t xml:space="preserve">Ngày hiệu lực:</t>
+    <t xml:space="preserve">Ngày hiệu lực: 01/06/2025</t>
   </si>
   <si>
     <t xml:space="preserve">CÔNG CHUẨN THÁNG VH</t>
@@ -37,9 +37,6 @@
     <t xml:space="preserve">CÔNG CHUẨN THÁNG VP</t>
   </si>
   <si>
-    <t xml:space="preserve">MẪU CHUẨN — PHF Payroll Canonical V1 (PHF_PAYROLL_TEMPLATE_VERSION=1). Điền dữ liệu nhân viên từ dòng 11 trở xuống. KHÔNG sửa 3 dòng tiêu đề (nhóm cột / tên cột / số thứ tự cột). Sau khi điền: Nhập bảng lương → Kiểm tra → (Đối chiếu cột nếu khác mẫu) → Xem trước → Xác nhận.</t>
-  </si>
-  <si>
     <t xml:space="preserve">TT</t>
   </si>
   <si>
@@ -331,624 +328,921 @@
     <t xml:space="preserve">BANK</t>
   </si>
 </sst>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0"/>
+  </numFmts>
+  <fonts count="6">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FF0B3F24"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF5C6672"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF0B3F24"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF8A94A0"/>
+      <name val="Calibri"/>
+    </font>
+  </fonts>
+  <fills count="4">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7B45"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F2EA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCBD5CF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCBD5CF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCBD5CF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCBD5CF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+</styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="11" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="13" customWidth="1"/>
+    <col min="16" max="16" width="13" customWidth="1"/>
+    <col min="17" max="17" width="13" customWidth="1"/>
+    <col min="18" max="18" width="13" customWidth="1"/>
+    <col min="19" max="19" width="13" customWidth="1"/>
+    <col min="20" max="20" width="13" customWidth="1"/>
+    <col min="21" max="21" width="13" customWidth="1"/>
+    <col min="22" max="22" width="13" customWidth="1"/>
+    <col min="23" max="23" width="13" customWidth="1"/>
+    <col min="24" max="24" width="13" customWidth="1"/>
+    <col min="25" max="25" width="13" customWidth="1"/>
+    <col min="26" max="26" width="13" customWidth="1"/>
+    <col min="27" max="27" width="13" customWidth="1"/>
+    <col min="28" max="28" width="13" customWidth="1"/>
+    <col min="29" max="29" width="13" customWidth="1"/>
+    <col min="30" max="30" width="13" customWidth="1"/>
+    <col min="31" max="31" width="13" customWidth="1"/>
+    <col min="32" max="32" width="13" customWidth="1"/>
+    <col min="33" max="33" width="13" customWidth="1"/>
+    <col min="34" max="34" width="13" customWidth="1"/>
+    <col min="35" max="35" width="13" customWidth="1"/>
+    <col min="36" max="36" width="13" customWidth="1"/>
+    <col min="37" max="37" width="13" customWidth="1"/>
+    <col min="38" max="38" width="13" customWidth="1"/>
+    <col min="39" max="39" width="13" customWidth="1"/>
+    <col min="40" max="40" width="13" customWidth="1"/>
+    <col min="41" max="41" width="13" customWidth="1"/>
+    <col min="42" max="42" width="13" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="13" customWidth="1"/>
+    <col min="45" max="45" width="13" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="13" customWidth="1"/>
+    <col min="48" max="48" width="13" customWidth="1"/>
+    <col min="49" max="49" width="13" customWidth="1"/>
+    <col min="50" max="50" width="13" customWidth="1"/>
+    <col min="51" max="51" width="13" customWidth="1"/>
+    <col min="52" max="52" width="13" customWidth="1"/>
+    <col min="53" max="53" width="13" customWidth="1"/>
+    <col min="54" max="54" width="13" customWidth="1"/>
+    <col min="55" max="55" width="13" customWidth="1"/>
+    <col min="56" max="56" width="13" customWidth="1"/>
+    <col min="57" max="57" width="13" customWidth="1"/>
+    <col min="58" max="58" width="13" customWidth="1"/>
+    <col min="59" max="59" width="13" customWidth="1"/>
+    <col min="60" max="60" width="13" customWidth="1"/>
+    <col min="61" max="61" width="13" customWidth="1"/>
+    <col min="62" max="62" width="13" customWidth="1"/>
+    <col min="63" max="63" width="13" customWidth="1"/>
+    <col min="64" max="64" width="13" customWidth="1"/>
+    <col min="65" max="65" width="13" customWidth="1"/>
+    <col min="66" max="66" width="13" customWidth="1"/>
+    <col min="67" max="67" width="13" customWidth="1"/>
+    <col min="68" max="68" width="13" customWidth="1"/>
+    <col min="69" max="69" width="13" customWidth="1"/>
+    <col min="70" max="70" width="13" customWidth="1"/>
+    <col min="71" max="71" width="13" customWidth="1"/>
+    <col min="72" max="72" width="13" customWidth="1"/>
+    <col min="73" max="73" width="13" customWidth="1"/>
+    <col min="74" max="74" width="13" customWidth="1"/>
+    <col min="75" max="75" width="13" customWidth="1"/>
+    <col min="76" max="76" width="13" customWidth="1"/>
+    <col min="77" max="77" width="11" customWidth="1"/>
+    <col min="78" max="78" width="11" customWidth="1"/>
+    <col min="79" max="79" width="13" customWidth="1"/>
+    <col min="80" max="80" width="13" customWidth="1"/>
+    <col min="81" max="81" width="13" customWidth="1"/>
+    <col min="82" max="82" width="13" customWidth="1"/>
+    <col min="83" max="83" width="13" customWidth="1"/>
+    <col min="84" max="84" width="13" customWidth="1"/>
+    <col min="85" max="85" width="11" customWidth="1"/>
+    <col min="86" max="86" width="13" customWidth="1"/>
+    <col min="87" max="87" width="11" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AJ2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3">
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AJ3" t="s">
+      <c r="AJ3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="K5" t="s">
+      <c r="K5" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6">
-      <c r="K6" t="s">
+      <c r="K6" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
+      <c r="G7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H7" t="s">
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="W8" s="3"/>
+      <c r="X8" s="3"/>
+      <c r="Y8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
+      <c r="AB8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC8" s="3"/>
+      <c r="AD8" s="3"/>
+      <c r="AE8" s="3"/>
+      <c r="AF8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG8" s="3"/>
+      <c r="AH8" s="3"/>
+      <c r="AI8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AJ8" s="3"/>
+      <c r="AK8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AL8" s="3"/>
+      <c r="AM8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AN8" s="3"/>
+      <c r="AO8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AP8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="AQ8" s="3"/>
+      <c r="AR8" s="3"/>
+      <c r="AS8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT8" s="3"/>
+      <c r="AU8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AV8" s="3"/>
+      <c r="AW8" s="3"/>
+      <c r="AX8" s="3"/>
+      <c r="AY8" s="3"/>
+      <c r="AZ8" s="3"/>
+      <c r="BA8" s="3"/>
+      <c r="BB8" s="3"/>
+      <c r="BC8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="BD8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="BE8" s="3"/>
+      <c r="BF8" s="3"/>
+      <c r="BG8" s="3"/>
+      <c r="BH8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="BJ8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="BK8" s="3"/>
+      <c r="BL8" s="3"/>
+      <c r="BM8" s="3"/>
+      <c r="BN8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="BO8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BP8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="BQ8" s="3"/>
+      <c r="BR8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="BS8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="BT8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="BU8" s="3"/>
+      <c r="BV8" s="3"/>
+      <c r="BW8" s="3"/>
+      <c r="BX8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="BY8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="BZ8" s="3"/>
+      <c r="CA8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="CB8" s="3"/>
+      <c r="CC8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="CD8" s="3"/>
+      <c r="CE8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="CF8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="CG8" s="3"/>
+      <c r="CH8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="CI8" s="3"/>
     </row>
-    <row r="8">
-      <c r="A8" t="s">
+    <row r="9" ht="64" customHeight="1">
+      <c r="A9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="S9" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="T9" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="W9" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="X9" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y9" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z9" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA9" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB9" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC9" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD9" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE9" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF9" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG9" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH9" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI9" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ9" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK9" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="AL9" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AM9" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN9" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO9" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP9" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AQ9" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR9" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="AS9" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT9" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU9" s="4"/>
+      <c r="AV9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AW9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AX9" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AZ9" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="BA9" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="BB9" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="BC9" s="4"/>
+      <c r="BD9" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="BE9" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="BF9" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="BG9" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="BH9" s="4"/>
+      <c r="BI9" s="4"/>
+      <c r="BJ9" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="BK9" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="BL9" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="BM9" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="BN9" s="4"/>
+      <c r="BO9" s="4"/>
+      <c r="BP9" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="BQ9" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="BR9" s="4"/>
+      <c r="BS9" s="4"/>
+      <c r="BT9" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="BU9" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="BV9" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="BW9" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="BX9" s="4"/>
+      <c r="BY9" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="BZ9" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="CA9" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="CB9" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="CC9" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="CD9" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="CE9" s="4"/>
+      <c r="CF9" s="4"/>
+      <c r="CG9" s="4"/>
+      <c r="CH9" s="4"/>
+      <c r="CI9" s="4"/>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5">
+        <v>2</v>
+      </c>
+      <c r="E10" s="5">
+        <v>3</v>
+      </c>
+      <c r="F10" s="5">
+        <v>4</v>
+      </c>
+      <c r="G10" s="5">
+        <v>5</v>
+      </c>
+      <c r="H10" s="5">
+        <v>6</v>
+      </c>
+      <c r="I10" s="5">
+        <v>7</v>
+      </c>
+      <c r="J10" s="5">
+        <v>8</v>
+      </c>
+      <c r="K10" s="5">
+        <v>9</v>
+      </c>
+      <c r="L10" s="5">
+        <v>10</v>
+      </c>
+      <c r="M10" s="5">
+        <v>11</v>
+      </c>
+      <c r="N10" s="5">
         <v>12</v>
       </c>
-      <c r="M8" t="s">
+      <c r="O10" s="5">
         <v>13</v>
       </c>
-      <c r="U8" t="s">
+      <c r="P10" s="5">
         <v>14</v>
       </c>
-      <c r="V8" t="s">
+      <c r="Q10" s="5">
         <v>15</v>
       </c>
-      <c r="Y8" t="s">
+      <c r="R10" s="5">
         <v>16</v>
       </c>
-      <c r="AB8" t="s">
+      <c r="S10" s="5">
         <v>17</v>
       </c>
-      <c r="AF8" t="s">
+      <c r="T10" s="5">
         <v>18</v>
       </c>
-      <c r="AI8" t="s">
+      <c r="U10" s="5">
         <v>19</v>
       </c>
-      <c r="AK8" t="s">
+      <c r="V10" s="5">
         <v>20</v>
       </c>
-      <c r="AM8" t="s">
+      <c r="W10" s="5">
         <v>21</v>
       </c>
-      <c r="AO8" t="s">
+      <c r="X10" s="5">
         <v>22</v>
       </c>
-      <c r="AP8" t="s">
+      <c r="Y10" s="5">
         <v>23</v>
       </c>
-      <c r="AS8" t="s">
+      <c r="Z10" s="5">
         <v>24</v>
       </c>
-      <c r="AU8" t="s">
+      <c r="AA10" s="5">
         <v>25</v>
       </c>
-      <c r="BC8" t="s">
+      <c r="AB10" s="5">
         <v>26</v>
       </c>
-      <c r="BD8" t="s">
+      <c r="AC10" s="5">
         <v>27</v>
       </c>
-      <c r="BH8" t="s">
+      <c r="AD10" s="5">
         <v>28</v>
       </c>
-      <c r="BI8" t="s">
+      <c r="AE10" s="5">
         <v>29</v>
       </c>
-      <c r="BJ8" t="s">
+      <c r="AF10" s="5">
         <v>30</v>
       </c>
-      <c r="BN8" t="s">
+      <c r="AG10" s="5">
         <v>31</v>
       </c>
-      <c r="BO8" t="s">
+      <c r="AH10" s="5">
         <v>32</v>
       </c>
-      <c r="BP8" t="s">
+      <c r="AI10" s="5">
         <v>33</v>
       </c>
-      <c r="BR8" t="s">
+      <c r="AJ10" s="5">
         <v>34</v>
       </c>
-      <c r="BS8" t="s">
+      <c r="AK10" s="5">
         <v>35</v>
       </c>
-      <c r="BT8" t="s">
+      <c r="AL10" s="5">
         <v>36</v>
       </c>
-      <c r="BX8" t="s">
+      <c r="AM10" s="5">
         <v>37</v>
       </c>
-      <c r="BY8" t="s">
+      <c r="AN10" s="5">
         <v>38</v>
       </c>
-      <c r="CA8" t="s">
+      <c r="AO10" s="5">
         <v>39</v>
       </c>
-      <c r="CC8" t="s">
+      <c r="AP10" s="5">
         <v>40</v>
       </c>
-      <c r="CE8" t="s">
+      <c r="AQ10" s="5">
         <v>41</v>
       </c>
-      <c r="CF8" t="s">
+      <c r="AR10" s="5">
         <v>42</v>
       </c>
-      <c r="CH8" t="s">
+      <c r="AS10" s="5">
         <v>43</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
+      <c r="AT10" s="5">
         <v>44</v>
       </c>
-      <c r="B9" t="s">
+      <c r="AU10" s="5">
         <v>45</v>
       </c>
-      <c r="C9" t="s">
+      <c r="AV10" s="5">
         <v>46</v>
       </c>
-      <c r="D9" t="s">
+      <c r="AW10" s="5">
         <v>47</v>
       </c>
-      <c r="E9" t="s">
+      <c r="AX10" s="5">
         <v>48</v>
       </c>
-      <c r="F9" t="s">
+      <c r="AY10" s="5">
         <v>49</v>
       </c>
-      <c r="G9" t="s">
+      <c r="AZ10" s="5">
         <v>50</v>
       </c>
-      <c r="H9" t="s">
+      <c r="BA10" s="5">
         <v>51</v>
       </c>
-      <c r="I9" t="s">
+      <c r="BB10" s="5">
         <v>52</v>
       </c>
-      <c r="J9" t="s">
+      <c r="BC10" s="5">
         <v>53</v>
       </c>
-      <c r="K9" t="s">
+      <c r="BD10" s="5">
         <v>54</v>
       </c>
-      <c r="L9" t="s">
+      <c r="BE10" s="5">
         <v>55</v>
       </c>
-      <c r="M9" t="s">
+      <c r="BF10" s="5">
         <v>56</v>
       </c>
-      <c r="N9" t="s">
+      <c r="BG10" s="5">
         <v>57</v>
       </c>
-      <c r="O9" t="s">
+      <c r="BH10" s="5">
         <v>58</v>
       </c>
-      <c r="P9" t="s">
+      <c r="BI10" s="5">
         <v>59</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="BJ10" s="5">
         <v>60</v>
       </c>
-      <c r="R9" t="s">
+      <c r="BK10" s="5">
         <v>61</v>
       </c>
-      <c r="S9" t="s">
+      <c r="BL10" s="5">
         <v>62</v>
       </c>
-      <c r="T9" t="s">
+      <c r="BM10" s="5">
         <v>63</v>
       </c>
-      <c r="V9" t="s">
+      <c r="BN10" s="5">
         <v>64</v>
       </c>
-      <c r="W9" t="s">
+      <c r="BO10" s="5">
         <v>65</v>
       </c>
-      <c r="X9" t="s">
+      <c r="BP10" s="5">
         <v>66</v>
       </c>
-      <c r="Y9" t="s">
+      <c r="BQ10" s="5">
         <v>67</v>
       </c>
-      <c r="Z9" t="s">
+      <c r="BR10" s="5">
         <v>68</v>
       </c>
-      <c r="AA9" t="s">
+      <c r="BS10" s="5">
         <v>69</v>
       </c>
-      <c r="AB9" t="s">
+      <c r="BT10" s="5">
         <v>70</v>
       </c>
-      <c r="AC9" t="s">
+      <c r="BU10" s="5">
         <v>71</v>
       </c>
-      <c r="AD9" t="s">
+      <c r="BV10" s="5">
         <v>72</v>
       </c>
-      <c r="AE9" t="s">
+      <c r="BW10" s="5">
         <v>73</v>
       </c>
-      <c r="AF9" t="s">
+      <c r="BX10" s="5">
         <v>74</v>
       </c>
-      <c r="AG9" t="s">
+      <c r="BY10" s="5">
         <v>75</v>
       </c>
-      <c r="AH9" t="s">
+      <c r="BZ10" s="5">
         <v>76</v>
       </c>
-      <c r="AI9" t="s">
+      <c r="CA10" s="5">
         <v>77</v>
       </c>
-      <c r="AJ9" t="s">
+      <c r="CB10" s="5">
         <v>78</v>
       </c>
-      <c r="AK9" t="s">
+      <c r="CC10" s="5">
         <v>79</v>
       </c>
-      <c r="AL9" t="s">
+      <c r="CD10" s="5">
         <v>80</v>
       </c>
-      <c r="AM9" t="s">
+      <c r="CE10" s="5">
         <v>81</v>
       </c>
-      <c r="AN9" t="s">
+      <c r="CF10" s="5">
         <v>82</v>
       </c>
-      <c r="AO9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AP9" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ9" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>85</v>
-      </c>
-      <c r="AS9" t="s">
-        <v>86</v>
-      </c>
-      <c r="AT9" t="s">
-        <v>87</v>
-      </c>
-      <c r="AV9" t="s">
-        <v>57</v>
-      </c>
-      <c r="AW9" t="s">
-        <v>58</v>
-      </c>
-      <c r="AX9" t="s">
-        <v>88</v>
-      </c>
-      <c r="AY9" t="s">
-        <v>60</v>
-      </c>
-      <c r="AZ9" t="s">
-        <v>61</v>
-      </c>
-      <c r="BA9" t="s">
-        <v>62</v>
-      </c>
-      <c r="BB9" t="s">
-        <v>89</v>
-      </c>
-      <c r="BD9" t="s">
-        <v>90</v>
-      </c>
-      <c r="BE9" t="s">
-        <v>91</v>
-      </c>
-      <c r="BF9" t="s">
-        <v>92</v>
-      </c>
-      <c r="BG9" t="s">
-        <v>93</v>
-      </c>
-      <c r="BJ9" t="s">
-        <v>94</v>
-      </c>
-      <c r="BK9" t="s">
-        <v>95</v>
-      </c>
-      <c r="BL9" t="s">
-        <v>96</v>
-      </c>
-      <c r="BM9" t="s">
-        <v>97</v>
-      </c>
-      <c r="BP9" t="s">
-        <v>98</v>
-      </c>
-      <c r="BQ9" t="s">
-        <v>89</v>
-      </c>
-      <c r="BT9" t="s">
-        <v>99</v>
-      </c>
-      <c r="BU9" t="s">
-        <v>100</v>
-      </c>
-      <c r="BV9" t="s">
-        <v>101</v>
-      </c>
-      <c r="BW9" t="s">
-        <v>102</v>
-      </c>
-      <c r="BY9" t="s">
-        <v>103</v>
-      </c>
-      <c r="BZ9" t="s">
-        <v>104</v>
-      </c>
-      <c r="CA9" t="s">
-        <v>103</v>
-      </c>
-      <c r="CB9" t="s">
-        <v>104</v>
-      </c>
-      <c r="CC9" t="s">
-        <v>105</v>
-      </c>
-      <c r="CD9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>2</v>
-      </c>
-      <c r="E10">
-        <v>3</v>
-      </c>
-      <c r="F10">
-        <v>4</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-      <c r="H10">
-        <v>6</v>
-      </c>
-      <c r="I10">
-        <v>7</v>
-      </c>
-      <c r="J10">
-        <v>8</v>
-      </c>
-      <c r="K10">
-        <v>9</v>
-      </c>
-      <c r="L10">
-        <v>10</v>
-      </c>
-      <c r="M10">
-        <v>11</v>
-      </c>
-      <c r="N10">
-        <v>12</v>
-      </c>
-      <c r="O10">
-        <v>13</v>
-      </c>
-      <c r="P10">
-        <v>14</v>
-      </c>
-      <c r="Q10">
-        <v>15</v>
-      </c>
-      <c r="R10">
-        <v>16</v>
-      </c>
-      <c r="S10">
-        <v>17</v>
-      </c>
-      <c r="T10">
-        <v>18</v>
-      </c>
-      <c r="U10">
-        <v>19</v>
-      </c>
-      <c r="V10">
-        <v>20</v>
-      </c>
-      <c r="W10">
-        <v>21</v>
-      </c>
-      <c r="X10">
-        <v>22</v>
-      </c>
-      <c r="Y10">
-        <v>23</v>
-      </c>
-      <c r="Z10">
-        <v>24</v>
-      </c>
-      <c r="AA10">
-        <v>25</v>
-      </c>
-      <c r="AB10">
-        <v>26</v>
-      </c>
-      <c r="AC10">
-        <v>27</v>
-      </c>
-      <c r="AD10">
-        <v>28</v>
-      </c>
-      <c r="AE10">
-        <v>29</v>
-      </c>
-      <c r="AF10">
-        <v>30</v>
-      </c>
-      <c r="AG10">
-        <v>31</v>
-      </c>
-      <c r="AH10">
-        <v>32</v>
-      </c>
-      <c r="AI10">
-        <v>33</v>
-      </c>
-      <c r="AJ10">
-        <v>34</v>
-      </c>
-      <c r="AK10">
-        <v>35</v>
-      </c>
-      <c r="AL10">
-        <v>36</v>
-      </c>
-      <c r="AM10">
-        <v>37</v>
-      </c>
-      <c r="AN10">
-        <v>38</v>
-      </c>
-      <c r="AO10">
-        <v>39</v>
-      </c>
-      <c r="AP10">
-        <v>40</v>
-      </c>
-      <c r="AQ10">
-        <v>41</v>
-      </c>
-      <c r="AR10">
-        <v>42</v>
-      </c>
-      <c r="AS10">
-        <v>43</v>
-      </c>
-      <c r="AT10">
-        <v>44</v>
-      </c>
-      <c r="AU10">
-        <v>45</v>
-      </c>
-      <c r="AV10">
-        <v>46</v>
-      </c>
-      <c r="AW10">
-        <v>47</v>
-      </c>
-      <c r="AX10">
-        <v>48</v>
-      </c>
-      <c r="AY10">
-        <v>49</v>
-      </c>
-      <c r="AZ10">
-        <v>50</v>
-      </c>
-      <c r="BA10">
-        <v>51</v>
-      </c>
-      <c r="BB10">
-        <v>52</v>
-      </c>
-      <c r="BC10">
-        <v>53</v>
-      </c>
-      <c r="BD10">
-        <v>54</v>
-      </c>
-      <c r="BE10">
-        <v>55</v>
-      </c>
-      <c r="BF10">
-        <v>56</v>
-      </c>
-      <c r="BG10">
-        <v>57</v>
-      </c>
-      <c r="BH10">
-        <v>58</v>
-      </c>
-      <c r="BI10">
-        <v>59</v>
-      </c>
-      <c r="BJ10">
-        <v>60</v>
-      </c>
-      <c r="BK10">
-        <v>61</v>
-      </c>
-      <c r="BL10">
-        <v>62</v>
-      </c>
-      <c r="BM10">
-        <v>63</v>
-      </c>
-      <c r="BN10">
-        <v>64</v>
-      </c>
-      <c r="BO10">
-        <v>65</v>
-      </c>
-      <c r="BP10">
-        <v>66</v>
-      </c>
-      <c r="BQ10">
-        <v>67</v>
-      </c>
-      <c r="BR10">
-        <v>68</v>
-      </c>
-      <c r="BS10">
-        <v>69</v>
-      </c>
-      <c r="BT10">
-        <v>70</v>
-      </c>
-      <c r="BU10">
-        <v>71</v>
-      </c>
-      <c r="BV10">
-        <v>72</v>
-      </c>
-      <c r="BW10">
-        <v>73</v>
-      </c>
-      <c r="BX10">
-        <v>74</v>
-      </c>
-      <c r="BY10">
-        <v>75</v>
-      </c>
-      <c r="BZ10">
-        <v>76</v>
-      </c>
-      <c r="CA10">
-        <v>77</v>
-      </c>
-      <c r="CB10">
-        <v>78</v>
-      </c>
-      <c r="CC10">
-        <v>79</v>
-      </c>
-      <c r="CD10">
-        <v>80</v>
-      </c>
-      <c r="CE10">
-        <v>81</v>
-      </c>
-      <c r="CF10">
-        <v>82</v>
-      </c>
+      <c r="CG10" s="5"/>
+      <c r="CH10" s="5"/>
+      <c r="CI10" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="M8:T8"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="AB8:AE8"/>
+    <mergeCell ref="AF8:AH8"/>
+    <mergeCell ref="AI8:AJ8"/>
+    <mergeCell ref="AK8:AL8"/>
+    <mergeCell ref="AM8:AN8"/>
+    <mergeCell ref="AP8:AR8"/>
+    <mergeCell ref="AS8:AT8"/>
+    <mergeCell ref="AU8:BB8"/>
+    <mergeCell ref="BD8:BG8"/>
+    <mergeCell ref="BJ8:BM8"/>
+    <mergeCell ref="BP8:BQ8"/>
+    <mergeCell ref="BT8:BW8"/>
+    <mergeCell ref="BY8:BZ8"/>
+    <mergeCell ref="CA8:CB8"/>
+    <mergeCell ref="CC8:CD8"/>
+    <mergeCell ref="CF8:CG8"/>
+    <mergeCell ref="CH8:CI8"/>
+  </mergeCells>
 </worksheet>
 </file>